--- a/portal/public/test-upload-template.xlsx
+++ b/portal/public/test-upload-template.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -428,7 +428,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -474,32 +474,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Option E (optional)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Passage</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Image</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Subtopic</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ideal time (sec)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Marks</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Negative Marks</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Concepts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -539,28 +579,26 @@
           <t>2% decrease</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1.2 × 0.8 = 0.96, so a 4% decrease.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Percentages</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,32 +616,26 @@
           <t>What is 15% of 200? (type-in: leave options empty)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.15 × 200 = 30.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Percentages</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -641,32 +673,31 @@
           <t>Fourth</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Explain the answer.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Paste the passage on every question of the set (or use a Set ID column).</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -704,22 +735,26 @@
           <t>…</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="L2:L5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Very Easy,Easy,Medium,Hard,Very Hard"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Single,Multiple,Numeric"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
